--- a/salidas/empresas/PEP.xlsx
+++ b/salidas/empresas/PEP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>31.21569442749023</v>
+        <v>31.2156925201416</v>
       </c>
       <c r="C2" t="n">
         <v>57.18000030517578</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>32.26932525634766</v>
+        <v>32.26933670043945</v>
       </c>
       <c r="C3" t="n">
         <v>59.11000061035156</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>31.68658065795898</v>
+        <v>31.68657875061035</v>
       </c>
       <c r="C4" t="n">
         <v>57.79000091552734</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>31.93331336975098</v>
+        <v>31.93331527709961</v>
       </c>
       <c r="C5" t="n">
         <v>58.2400016784668</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.08425903320312</v>
+        <v>33.08426284790039</v>
       </c>
       <c r="C7" t="n">
         <v>60.04000091552734</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.92471694946289</v>
+        <v>34.92472457885742</v>
       </c>
       <c r="C8" t="n">
         <v>63.38000106811523</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.97169494628906</v>
+        <v>35.97168731689453</v>
       </c>
       <c r="C9" t="n">
         <v>65.27999877929688</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>36.12689590454102</v>
+        <v>36.12689971923828</v>
       </c>
       <c r="C10" t="n">
         <v>65.26000213623047</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>35.11938858032227</v>
+        <v>35.1193733215332</v>
       </c>
       <c r="C11" t="n">
         <v>63.43999862670898</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>34.30560302734375</v>
+        <v>34.30561065673828</v>
       </c>
       <c r="C12" t="n">
         <v>61.97000122070312</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>36.28545761108398</v>
+        <v>36.28546524047852</v>
       </c>
       <c r="C14" t="n">
         <v>65.23999786376953</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>35.12303161621094</v>
+        <v>35.12303924560547</v>
       </c>
       <c r="C15" t="n">
         <v>63.15000152587891</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>35.51951217651367</v>
+        <v>35.51950073242188</v>
       </c>
       <c r="C16" t="n">
         <v>63.56000137329102</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>36.93338012695312</v>
+        <v>36.93337631225586</v>
       </c>
       <c r="C17" t="n">
         <v>66.08999633789062</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>38.18516540527344</v>
+        <v>38.18515396118164</v>
       </c>
       <c r="C18" t="n">
         <v>68.33000183105469</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>36.87521743774414</v>
+        <v>36.87522506713867</v>
       </c>
       <c r="C20" t="n">
         <v>65.62000274658203</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>38.22951507568359</v>
+        <v>38.22952651977539</v>
       </c>
       <c r="C21" t="n">
         <v>68.02999877929688</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>41.39477920532227</v>
+        <v>41.39477157592773</v>
       </c>
       <c r="C22" t="n">
         <v>73.26000213623047</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>41.65468978881836</v>
+        <v>41.65470886230469</v>
       </c>
       <c r="C23" t="n">
         <v>73.72000122070312</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>43.60972213745117</v>
+        <v>43.6097297668457</v>
       </c>
       <c r="C24" t="n">
         <v>77.18000030517578</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>43.09732055664062</v>
+        <v>43.09730911254883</v>
       </c>
       <c r="C25" t="n">
         <v>75.90000152587891</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>38.63995742797852</v>
+        <v>38.63996505737305</v>
       </c>
       <c r="C26" t="n">
         <v>68.05000305175781</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>39.49735260009766</v>
+        <v>39.49736785888672</v>
       </c>
       <c r="C27" t="n">
         <v>69.55999755859375</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>41.21707534790039</v>
+        <v>41.21707153320312</v>
       </c>
       <c r="C28" t="n">
         <v>72.19999694824219</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>39.12197494506836</v>
+        <v>39.12199020385742</v>
       </c>
       <c r="C29" t="n">
         <v>68.52999877929688</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>38.99067687988281</v>
+        <v>38.99067306518555</v>
       </c>
       <c r="C30" t="n">
         <v>68.30000305175781</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>36.53341293334961</v>
+        <v>36.53342056274414</v>
       </c>
       <c r="C31" t="n">
         <v>63.59000015258789</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>38.2397346496582</v>
+        <v>38.23975372314453</v>
       </c>
       <c r="C32" t="n">
         <v>66.55999755859375</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>39.34281158447266</v>
+        <v>39.34281921386719</v>
       </c>
       <c r="C33" t="n">
         <v>68.48000335693359</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>41.19776916503906</v>
+        <v>41.19777297973633</v>
       </c>
       <c r="C34" t="n">
         <v>71.26999664306641</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>32.95474624633789</v>
+        <v>32.95475387573242</v>
       </c>
       <c r="C35" t="n">
         <v>57.0099983215332</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>32.77554702758789</v>
+        <v>32.77555465698242</v>
       </c>
       <c r="C36" t="n">
         <v>56.70000076293945</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>31.90896987915039</v>
+        <v>31.90896606445312</v>
       </c>
       <c r="C37" t="n">
         <v>54.77000045776367</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>29.26397132873535</v>
+        <v>29.26397705078125</v>
       </c>
       <c r="C38" t="n">
         <v>50.22999954223633</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>28.04633712768555</v>
+        <v>28.04635429382324</v>
       </c>
       <c r="C39" t="n">
         <v>48.13999938964844</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>30.25752639770508</v>
+        <v>30.25754165649414</v>
       </c>
       <c r="C40" t="n">
         <v>51.47999954223633</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>29.2465934753418</v>
+        <v>29.24660301208496</v>
       </c>
       <c r="C41" t="n">
         <v>49.7599983215332</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>30.59255027770996</v>
+        <v>30.59255790710449</v>
       </c>
       <c r="C42" t="n">
         <v>52.04999923706055</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>32.56758880615234</v>
+        <v>32.56758499145508</v>
       </c>
       <c r="C43" t="n">
         <v>54.95999908447266</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>33.6282958984375</v>
+        <v>33.6282844543457</v>
       </c>
       <c r="C44" t="n">
         <v>56.75</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>33.58087539672852</v>
+        <v>33.58090209960938</v>
       </c>
       <c r="C45" t="n">
         <v>56.66999816894531</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>35.04042434692383</v>
+        <v>35.0404167175293</v>
       </c>
       <c r="C46" t="n">
         <v>58.65999984741211</v>
@@ -1337,7 +1349,7 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1362,11 +1374,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>37.16698455810547</v>
+        <v>37.16698837280273</v>
       </c>
       <c r="C48" t="n">
         <v>62.22000122070312</v>
@@ -1387,11 +1399,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>36.57644653320312</v>
+        <v>36.57646942138672</v>
       </c>
       <c r="C49" t="n">
         <v>60.79999923706055</v>
@@ -1412,11 +1424,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>35.86656951904297</v>
+        <v>35.8665771484375</v>
       </c>
       <c r="C50" t="n">
         <v>59.61999893188477</v>
@@ -1437,11 +1449,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>37.58111190795898</v>
+        <v>37.58110427856445</v>
       </c>
       <c r="C51" t="n">
         <v>62.47000122070312</v>
@@ -1462,11 +1474,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>40.08368301391602</v>
+        <v>40.08368682861328</v>
       </c>
       <c r="C52" t="n">
         <v>66.16000366210938</v>
@@ -1487,11 +1499,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>39.51415634155273</v>
+        <v>39.5141716003418</v>
       </c>
       <c r="C53" t="n">
         <v>65.22000122070312</v>
@@ -1512,11 +1524,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>38.10253143310547</v>
+        <v>38.10251235961914</v>
       </c>
       <c r="C54" t="n">
         <v>62.88999938964844</v>
@@ -1537,11 +1549,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>37.21176147460938</v>
+        <v>37.21174621582031</v>
       </c>
       <c r="C55" t="n">
         <v>60.95000076293945</v>
@@ -1562,11 +1574,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>39.62944412231445</v>
+        <v>39.62945175170898</v>
       </c>
       <c r="C56" t="n">
         <v>64.91000366210938</v>
@@ -1587,11 +1599,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>39.18376159667969</v>
+        <v>39.18375396728516</v>
       </c>
       <c r="C57" t="n">
         <v>64.18000030517578</v>
@@ -1612,11 +1624,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>40.86922836303711</v>
+        <v>40.86921310424805</v>
       </c>
       <c r="C58" t="n">
         <v>66.44000244140625</v>
@@ -1637,11 +1649,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>40.16796493530273</v>
+        <v>40.16796875</v>
       </c>
       <c r="C59" t="n">
         <v>65.30000305175781</v>
@@ -1662,11 +1674,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>39.75583648681641</v>
+        <v>39.75583267211914</v>
       </c>
       <c r="C60" t="n">
         <v>64.62999725341797</v>
@@ -1687,11 +1699,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>40.48711776733398</v>
+        <v>40.48710250854492</v>
       </c>
       <c r="C61" t="n">
         <v>65.33000183105469</v>
@@ -1712,11 +1724,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>39.85497665405273</v>
+        <v>39.85498046875</v>
       </c>
       <c r="C62" t="n">
         <v>64.30999755859375</v>
@@ -1737,11 +1749,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>39.30342864990234</v>
+        <v>39.30343627929688</v>
       </c>
       <c r="C63" t="n">
         <v>63.41999816894531</v>
@@ -1766,11 +1778,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>40.22240447998047</v>
+        <v>40.2224006652832</v>
       </c>
       <c r="C64" t="n">
         <v>64.41000366210938</v>
@@ -1795,11 +1807,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>43.02005004882812</v>
+        <v>43.02003860473633</v>
       </c>
       <c r="C65" t="n">
         <v>68.88999938964844</v>
@@ -1824,11 +1836,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>44.41262817382812</v>
+        <v>44.41261672973633</v>
       </c>
       <c r="C66" t="n">
         <v>71.12000274658203</v>
@@ -1853,11 +1865,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>44.30255126953125</v>
+        <v>44.30255889892578</v>
       </c>
       <c r="C67" t="n">
         <v>70.43000030517578</v>
@@ -1882,11 +1894,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>40.28304672241211</v>
+        <v>40.28305053710938</v>
       </c>
       <c r="C68" t="n">
         <v>64.04000091552734</v>
@@ -1911,11 +1923,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>40.85446166992188</v>
+        <v>40.85446929931641</v>
       </c>
       <c r="C69" t="n">
         <v>64.43000030517578</v>
@@ -1940,7 +1952,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1969,11 +1981,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>39.91600799560547</v>
+        <v>39.9160270690918</v>
       </c>
       <c r="C71" t="n">
         <v>62.95000076293945</v>
@@ -1998,11 +2010,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>40.91279220581055</v>
+        <v>40.91278457641602</v>
       </c>
       <c r="C72" t="n">
         <v>64</v>
@@ -2027,7 +2039,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2056,11 +2068,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.98035430908203</v>
+        <v>41.9803581237793</v>
       </c>
       <c r="C74" t="n">
         <v>65.66999816894531</v>
@@ -2085,11 +2097,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>40.56509399414062</v>
+        <v>40.56510162353516</v>
       </c>
       <c r="C75" t="n">
         <v>62.93999862670898</v>
@@ -2114,11 +2126,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>42.76284408569336</v>
+        <v>42.76285934448242</v>
       </c>
       <c r="C76" t="n">
         <v>66.34999847412109</v>
@@ -2143,11 +2155,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>42.53727722167969</v>
+        <v>42.53727340698242</v>
       </c>
       <c r="C77" t="n">
         <v>66</v>
@@ -2172,7 +2184,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2201,7 +2213,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2230,11 +2242,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>47.24137878417969</v>
+        <v>47.24140930175781</v>
       </c>
       <c r="C80" t="n">
         <v>72.73000335693359</v>
@@ -2259,11 +2271,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>47.04653167724609</v>
+        <v>47.04652786254883</v>
       </c>
       <c r="C81" t="n">
         <v>72.43000030517578</v>
@@ -2288,7 +2300,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2317,11 +2329,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>45.31080627441406</v>
+        <v>45.31081390380859</v>
       </c>
       <c r="C83" t="n">
         <v>69.23999786376953</v>
@@ -2346,11 +2358,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>45.9455680847168</v>
+        <v>45.94557571411133</v>
       </c>
       <c r="C84" t="n">
         <v>70.20999908447266</v>
@@ -2375,11 +2387,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>45.12762451171875</v>
+        <v>45.12762069702148</v>
       </c>
       <c r="C85" t="n">
         <v>68.43000030517578</v>
@@ -2404,7 +2416,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2433,11 +2445,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>50.32552337646484</v>
+        <v>50.32553100585938</v>
       </c>
       <c r="C87" t="n">
         <v>75.76999664306641</v>
@@ -2462,11 +2474,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.54393005371094</v>
+        <v>52.54389953613281</v>
       </c>
       <c r="C88" t="n">
         <v>79.11000061035156</v>
@@ -2491,11 +2503,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>54.77557373046875</v>
+        <v>54.77559661865234</v>
       </c>
       <c r="C89" t="n">
         <v>82.47000122070312</v>
@@ -2520,11 +2532,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>53.6464729309082</v>
+        <v>53.64646530151367</v>
       </c>
       <c r="C90" t="n">
         <v>80.76999664306641</v>
@@ -2549,7 +2561,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2578,11 +2590,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>55.87505722045898</v>
+        <v>55.87505340576172</v>
       </c>
       <c r="C92" t="n">
         <v>83.54000091552734</v>
@@ -2607,11 +2619,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>53.32677459716797</v>
+        <v>53.32676315307617</v>
       </c>
       <c r="C93" t="n">
         <v>79.73000335693359</v>
@@ -2636,11 +2648,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>53.55218124389648</v>
+        <v>53.55221176147461</v>
       </c>
       <c r="C94" t="n">
         <v>79.5</v>
@@ -2665,11 +2677,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>56.64408874511719</v>
+        <v>56.64408493041992</v>
       </c>
       <c r="C95" t="n">
         <v>84.08999633789062</v>
@@ -2694,11 +2706,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>56.89332962036133</v>
+        <v>56.89331817626953</v>
       </c>
       <c r="C96" t="n">
         <v>84.45999908447266</v>
@@ -2723,11 +2735,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>56.25070571899414</v>
+        <v>56.25071716308594</v>
       </c>
       <c r="C97" t="n">
         <v>82.94000244140625</v>
@@ -2752,11 +2764,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>54.50094223022461</v>
+        <v>54.50092315673828</v>
       </c>
       <c r="C98" t="n">
         <v>80.36000061035156</v>
@@ -2781,11 +2793,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>54.30423355102539</v>
+        <v>54.30425643920898</v>
       </c>
       <c r="C99" t="n">
         <v>80.06999969482422</v>
@@ -2810,11 +2822,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>57.03116607666016</v>
+        <v>57.03115081787109</v>
       </c>
       <c r="C100" t="n">
         <v>83.5</v>
@@ -2839,11 +2851,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>58.66353225708008</v>
+        <v>58.66353607177734</v>
       </c>
       <c r="C101" t="n">
         <v>85.88999938964844</v>
@@ -2868,7 +2880,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2897,11 +2909,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>61.47636032104492</v>
+        <v>61.47637939453125</v>
       </c>
       <c r="C103" t="n">
         <v>89.33999633789062</v>
@@ -2926,11 +2938,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>60.62311172485352</v>
+        <v>60.62311935424805</v>
       </c>
       <c r="C104" t="n">
         <v>88.09999847412109</v>
@@ -2955,11 +2967,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>63.6439323425293</v>
+        <v>63.6439208984375</v>
       </c>
       <c r="C105" t="n">
         <v>92.48999786376953</v>
@@ -2984,11 +2996,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>64.51374816894531</v>
+        <v>64.51375579833984</v>
       </c>
       <c r="C106" t="n">
         <v>93.08999633789062</v>
@@ -3013,11 +3025,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>66.64825439453125</v>
+        <v>66.64826965332031</v>
       </c>
       <c r="C107" t="n">
         <v>96.16999816894531</v>
@@ -3042,11 +3054,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>69.37184906005859</v>
+        <v>69.37184143066406</v>
       </c>
       <c r="C108" t="n">
         <v>100.0999984741211</v>
@@ -3071,11 +3083,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>65.96283721923828</v>
+        <v>65.96286773681641</v>
       </c>
       <c r="C109" t="n">
         <v>94.55999755859375</v>
@@ -3100,11 +3112,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>65.41877746582031</v>
+        <v>65.41874694824219</v>
       </c>
       <c r="C110" t="n">
         <v>93.77999877929688</v>
@@ -3129,11 +3141,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>69.04616546630859</v>
+        <v>69.04618072509766</v>
       </c>
       <c r="C111" t="n">
         <v>98.98000335693359</v>
@@ -3158,11 +3170,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>67.14926910400391</v>
+        <v>67.14928436279297</v>
       </c>
       <c r="C112" t="n">
         <v>95.62000274658203</v>
@@ -3187,7 +3199,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3216,11 +3228,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>67.71809387207031</v>
+        <v>67.71811676025391</v>
       </c>
       <c r="C114" t="n">
         <v>96.43000030517578</v>
@@ -3245,7 +3257,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3274,11 +3286,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>68.16079711914062</v>
+        <v>68.1607666015625</v>
       </c>
       <c r="C116" t="n">
         <v>96.34999847412109</v>
@@ -3303,11 +3315,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>65.74138641357422</v>
+        <v>65.74139404296875</v>
       </c>
       <c r="C117" t="n">
         <v>92.93000030517578</v>
@@ -3332,11 +3344,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>67.22806549072266</v>
+        <v>67.22805023193359</v>
       </c>
       <c r="C118" t="n">
         <v>94.30000305175781</v>
@@ -3361,11 +3373,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>72.85298156738281</v>
+        <v>72.85294342041016</v>
       </c>
       <c r="C119" t="n">
         <v>102.1900024414062</v>
@@ -3390,11 +3402,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>71.40575408935547</v>
+        <v>71.40570068359375</v>
       </c>
       <c r="C120" t="n">
         <v>100.1600036621094</v>
@@ -3419,11 +3431,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>71.73365020751953</v>
+        <v>71.733642578125</v>
       </c>
       <c r="C121" t="n">
         <v>99.91999816894531</v>
@@ -3448,11 +3460,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>71.28851318359375</v>
+        <v>71.28852844238281</v>
       </c>
       <c r="C122" t="n">
         <v>99.30000305175781</v>
@@ -3477,7 +3489,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3506,11 +3518,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>74.09716796875</v>
+        <v>74.09714508056641</v>
       </c>
       <c r="C124" t="n">
         <v>102.4800033569336</v>
@@ -3535,11 +3547,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>74.44424438476562</v>
+        <v>74.44425201416016</v>
       </c>
       <c r="C125" t="n">
         <v>102.9599990844727</v>
@@ -3564,11 +3576,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>73.14997863769531</v>
+        <v>73.14998626708984</v>
       </c>
       <c r="C126" t="n">
         <v>101.1699981689453</v>
@@ -3593,11 +3605,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>77.17328643798828</v>
+        <v>77.17329406738281</v>
       </c>
       <c r="C127" t="n">
         <v>105.9400024414062</v>
@@ -3622,11 +3634,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>79.34410095214844</v>
+        <v>79.34410858154297</v>
       </c>
       <c r="C128" t="n">
         <v>108.9199981689453</v>
@@ -3651,11 +3663,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>78.31336975097656</v>
+        <v>78.31338500976562</v>
       </c>
       <c r="C129" t="n">
         <v>106.75</v>
@@ -3680,11 +3692,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>79.79528045654297</v>
+        <v>79.79527282714844</v>
       </c>
       <c r="C130" t="n">
         <v>108.7699966430664</v>
@@ -3709,11 +3721,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>78.64347076416016</v>
+        <v>78.64347839355469</v>
       </c>
       <c r="C131" t="n">
         <v>107.1999969482422</v>
@@ -3738,7 +3750,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3767,11 +3779,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>77.32595062255859</v>
+        <v>77.32595825195312</v>
       </c>
       <c r="C133" t="n">
         <v>104.629997253418</v>
@@ -3796,7 +3808,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3825,11 +3837,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>81.57542419433594</v>
+        <v>81.575439453125</v>
       </c>
       <c r="C135" t="n">
         <v>110.379997253418</v>
@@ -3854,11 +3866,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>83.23704528808594</v>
+        <v>83.237060546875</v>
       </c>
       <c r="C136" t="n">
         <v>111.8600006103516</v>
@@ -3883,7 +3895,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3912,11 +3924,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>87.5623779296875</v>
+        <v>87.56240081787109</v>
       </c>
       <c r="C138" t="n">
         <v>116.870002746582</v>
@@ -3941,7 +3953,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3970,7 +3982,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3999,11 +4011,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>87.3150634765625</v>
+        <v>87.31505584716797</v>
       </c>
       <c r="C141" t="n">
         <v>115.7300033569336</v>
@@ -4028,11 +4040,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>84.07081604003906</v>
+        <v>84.07082366943359</v>
       </c>
       <c r="C142" t="n">
         <v>111.4300003051758</v>
@@ -4057,11 +4069,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>83.16545867919922</v>
+        <v>83.16547393798828</v>
       </c>
       <c r="C143" t="n">
         <v>110.2300033569336</v>
@@ -4086,11 +4098,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>88.52098083496094</v>
+        <v>88.52095031738281</v>
       </c>
       <c r="C144" t="n">
         <v>116.5199966430664</v>
@@ -4115,11 +4127,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>91.10397338867188</v>
+        <v>91.10396575927734</v>
       </c>
       <c r="C145" t="n">
         <v>119.9199981689453</v>
@@ -4144,11 +4156,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>91.39264678955078</v>
+        <v>91.39267730712891</v>
       </c>
       <c r="C146" t="n">
         <v>120.3000030517578</v>
@@ -4173,11 +4185,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>83.36256408691406</v>
+        <v>83.36257934570312</v>
       </c>
       <c r="C147" t="n">
         <v>109.7300033569336</v>
@@ -4202,7 +4214,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4231,11 +4243,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>77.25147247314453</v>
+        <v>77.25150299072266</v>
       </c>
       <c r="C149" t="n">
         <v>100.9400024414062</v>
@@ -4260,7 +4272,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4289,11 +4301,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>84.08677673339844</v>
+        <v>84.08676147460938</v>
       </c>
       <c r="C151" t="n">
         <v>108.870002746582</v>
@@ -4318,7 +4330,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4347,11 +4359,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>86.51198577880859</v>
+        <v>86.51197052001953</v>
       </c>
       <c r="C153" t="n">
         <v>112.0100021362305</v>
@@ -4376,7 +4388,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4405,7 +4417,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4434,11 +4446,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>94.96052551269531</v>
+        <v>94.96056365966797</v>
       </c>
       <c r="C156" t="n">
         <v>121.9400024414062</v>
@@ -4463,11 +4475,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>86.71925354003906</v>
+        <v>86.71923065185547</v>
       </c>
       <c r="C157" t="n">
         <v>110.4800033569336</v>
@@ -4492,11 +4504,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>88.43824768066406</v>
+        <v>88.438232421875</v>
       </c>
       <c r="C158" t="n">
         <v>112.6699981689453</v>
@@ -4521,11 +4533,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>91.50553131103516</v>
+        <v>91.50554656982422</v>
       </c>
       <c r="C159" t="n">
         <v>115.6399993896484</v>
@@ -4550,11 +4562,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>96.97340393066406</v>
+        <v>96.97339630126953</v>
       </c>
       <c r="C160" t="n">
         <v>122.5500030517578</v>
@@ -4579,11 +4591,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>101.3255081176758</v>
+        <v>101.3255233764648</v>
       </c>
       <c r="C161" t="n">
         <v>128.0500030517578</v>
@@ -4608,11 +4620,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>101.2859497070312</v>
+        <v>101.2859573364258</v>
       </c>
       <c r="C162" t="n">
         <v>128</v>
@@ -4637,11 +4649,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>104.5224151611328</v>
+        <v>104.5224533081055</v>
       </c>
       <c r="C163" t="n">
         <v>131.1300048828125</v>
@@ -4666,11 +4678,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>101.876106262207</v>
+        <v>101.876091003418</v>
       </c>
       <c r="C164" t="n">
         <v>127.8099975585938</v>
@@ -4695,11 +4707,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>108.9861221313477</v>
+        <v>108.9861297607422</v>
       </c>
       <c r="C165" t="n">
         <v>136.7299957275391</v>
@@ -4724,11 +4736,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>110.0362167358398</v>
+        <v>110.0362701416016</v>
       </c>
       <c r="C166" t="n">
         <v>137.1000061035156</v>
@@ -4753,7 +4765,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4782,11 +4794,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>109.0169448852539</v>
+        <v>109.0169372558594</v>
       </c>
       <c r="C168" t="n">
         <v>135.8300018310547</v>
@@ -4811,11 +4823,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>110.4594497680664</v>
+        <v>110.4594268798828</v>
       </c>
       <c r="C169" t="n">
         <v>136.6699981689453</v>
@@ -4840,11 +4852,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>114.7834091186523</v>
+        <v>114.7833938598633</v>
       </c>
       <c r="C170" t="n">
         <v>142.0200042724609</v>
@@ -4869,11 +4881,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>106.7092895507812</v>
+        <v>106.7092971801758</v>
       </c>
       <c r="C171" t="n">
         <v>132.0299987792969</v>
@@ -4898,11 +4910,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>97.72267913818359</v>
+        <v>97.72266387939453</v>
       </c>
       <c r="C172" t="n">
         <v>120.0999984741211</v>
@@ -4927,11 +4939,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>107.6413726806641</v>
+        <v>107.6413803100586</v>
       </c>
       <c r="C173" t="n">
         <v>132.2899932861328</v>
@@ -4956,11 +4968,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>107.0392532348633</v>
+        <v>107.0392608642578</v>
       </c>
       <c r="C174" t="n">
         <v>131.5500030517578</v>
@@ -4985,11 +4997,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>108.4523010253906</v>
+        <v>108.4522933959961</v>
       </c>
       <c r="C175" t="n">
         <v>132.2599945068359</v>
@@ -5014,7 +5026,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>114.8482208251953</v>
+        <v>114.8482437133789</v>
       </c>
       <c r="C177" t="n">
         <v>140.0599975585938</v>
@@ -5072,11 +5084,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>114.46826171875</v>
+        <v>114.4682693481445</v>
       </c>
       <c r="C178" t="n">
         <v>138.6000061035156</v>
@@ -5101,7 +5113,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5130,11 +5142,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>119.1180191040039</v>
+        <v>119.1180419921875</v>
       </c>
       <c r="C180" t="n">
         <v>144.2299957275391</v>
@@ -5159,11 +5171,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>123.3519668579102</v>
+        <v>123.3519287109375</v>
       </c>
       <c r="C181" t="n">
         <v>148.3000030517578</v>
@@ -5188,11 +5200,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>113.5952758789062</v>
+        <v>113.5952453613281</v>
       </c>
       <c r="C182" t="n">
         <v>136.5700073242188</v>
@@ -5217,11 +5229,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>107.4567718505859</v>
+        <v>107.4567565917969</v>
       </c>
       <c r="C183" t="n">
         <v>129.1900024414062</v>
@@ -5246,11 +5258,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>118.5937728881836</v>
+        <v>118.5937881469727</v>
       </c>
       <c r="C184" t="n">
         <v>141.4499969482422</v>
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>120.8659057617188</v>
+        <v>120.8658981323242</v>
       </c>
       <c r="C185" t="n">
         <v>144.1600036621094</v>
@@ -5304,11 +5316,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>124.0350570678711</v>
+        <v>124.0350723266602</v>
       </c>
       <c r="C186" t="n">
         <v>147.9400024414062</v>
@@ -5333,11 +5345,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>125.1355285644531</v>
+        <v>125.135498046875</v>
       </c>
       <c r="C187" t="n">
         <v>148.1699981689453</v>
@@ -5362,11 +5374,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>132.550537109375</v>
+        <v>132.5505523681641</v>
       </c>
       <c r="C188" t="n">
         <v>156.9499969482422</v>
@@ -5391,11 +5403,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>132.0776214599609</v>
+        <v>132.0776062011719</v>
       </c>
       <c r="C189" t="n">
         <v>156.3899993896484</v>
@@ -5420,11 +5432,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>127.89794921875</v>
+        <v>127.8979797363281</v>
       </c>
       <c r="C190" t="n">
         <v>150.4100036621094</v>
@@ -5449,11 +5461,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>137.4131317138672</v>
+        <v>137.4131469726562</v>
       </c>
       <c r="C191" t="n">
         <v>161.6000061035156</v>
@@ -5478,11 +5490,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>135.8655090332031</v>
+        <v>135.8655242919922</v>
       </c>
       <c r="C192" t="n">
         <v>159.7799987792969</v>
@@ -5507,11 +5519,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>148.7087707519531</v>
+        <v>148.708740234375</v>
       </c>
       <c r="C193" t="n">
         <v>173.7100067138672</v>
@@ -5536,7 +5548,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5565,11 +5577,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>140.1736755371094</v>
+        <v>140.1736907958984</v>
       </c>
       <c r="C195" t="n">
         <v>163.7400054931641</v>
@@ -5594,11 +5606,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>144.2322235107422</v>
+        <v>144.2322387695312</v>
       </c>
       <c r="C196" t="n">
         <v>167.3800048828125</v>
@@ -5623,11 +5635,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>147.9634399414062</v>
+        <v>147.9634246826172</v>
       </c>
       <c r="C197" t="n">
         <v>171.7100067138672</v>
@@ -5652,11 +5664,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>144.5510711669922</v>
+        <v>144.5510559082031</v>
       </c>
       <c r="C198" t="n">
         <v>167.75</v>
@@ -5681,11 +5693,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>144.6106719970703</v>
+        <v>144.6106872558594</v>
       </c>
       <c r="C199" t="n">
         <v>166.6600036621094</v>
@@ -5710,7 +5722,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5739,11 +5751,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>149.4784698486328</v>
+        <v>149.4784851074219</v>
       </c>
       <c r="C201" t="n">
         <v>172.2700042724609</v>
@@ -5768,11 +5780,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>142.6125335693359</v>
+        <v>142.6125030517578</v>
       </c>
       <c r="C202" t="n">
         <v>163.2599945068359</v>
@@ -5797,11 +5809,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>158.6155700683594</v>
+        <v>158.6156158447266</v>
       </c>
       <c r="C203" t="n">
         <v>181.5800018310547</v>
@@ -5826,11 +5838,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>162.0485687255859</v>
+        <v>162.0485992431641</v>
       </c>
       <c r="C204" t="n">
         <v>185.5099945068359</v>
@@ -5855,7 +5867,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5884,11 +5896,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>150.3230133056641</v>
+        <v>150.3229827880859</v>
       </c>
       <c r="C206" t="n">
         <v>171.0200042724609</v>
@@ -5913,7 +5925,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5942,11 +5954,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>161.3206634521484</v>
+        <v>161.3207092285156</v>
       </c>
       <c r="C208" t="n">
         <v>182.3000030517578</v>
@@ -5971,7 +5983,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6000,11 +6012,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>161.3649444580078</v>
+        <v>161.3649291992188</v>
       </c>
       <c r="C210" t="n">
         <v>182.3500061035156</v>
@@ -6029,11 +6041,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>165.0496215820312</v>
+        <v>165.0496520996094</v>
       </c>
       <c r="C211" t="n">
         <v>185.2200012207031</v>
@@ -6058,11 +6070,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>167.0457000732422</v>
+        <v>167.0456695556641</v>
       </c>
       <c r="C212" t="n">
         <v>187.4600067138672</v>
@@ -6087,7 +6099,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6116,11 +6128,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>152.0502319335938</v>
+        <v>152.0502471923828</v>
       </c>
       <c r="C214" t="n">
         <v>169.4400024414062</v>
@@ -6145,11 +6157,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>146.5224761962891</v>
+        <v>146.5224609375</v>
       </c>
       <c r="C215" t="n">
         <v>163.2799987792969</v>
@@ -6174,11 +6186,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>152.1698303222656</v>
+        <v>152.1698455810547</v>
       </c>
       <c r="C216" t="n">
         <v>168.2899932861328</v>
@@ -6203,7 +6215,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6232,11 +6244,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>152.3868560791016</v>
+        <v>152.3868865966797</v>
       </c>
       <c r="C218" t="n">
         <v>168.5299987792969</v>
@@ -6261,11 +6273,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>150.643310546875</v>
+        <v>150.6433258056641</v>
       </c>
       <c r="C219" t="n">
         <v>165.3399963378906</v>
@@ -6290,11 +6302,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>159.4537811279297</v>
+        <v>159.4537658691406</v>
       </c>
       <c r="C220" t="n">
         <v>175.0099945068359</v>
@@ -6319,7 +6331,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6348,7 +6360,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6377,11 +6389,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>151.4546508789062</v>
+        <v>151.4546661376953</v>
       </c>
       <c r="C223" t="n">
         <v>164.9299926757812</v>
@@ -6406,11 +6418,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>158.562255859375</v>
+        <v>158.5622711181641</v>
       </c>
       <c r="C224" t="n">
         <v>172.6699981689453</v>
@@ -6435,11 +6447,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>158.7550811767578</v>
+        <v>158.7550964355469</v>
       </c>
       <c r="C225" t="n">
         <v>172.8800048828125</v>
@@ -6464,11 +6476,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>157.3454132080078</v>
+        <v>157.3453979492188</v>
       </c>
       <c r="C226" t="n">
         <v>170.0500030517578</v>
@@ -6493,11 +6505,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>153.6720275878906</v>
+        <v>153.6720123291016</v>
       </c>
       <c r="C227" t="n">
         <v>166.0800018310547</v>
@@ -6522,11 +6534,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>151.2385101318359</v>
+        <v>151.2384948730469</v>
       </c>
       <c r="C228" t="n">
         <v>163.4499969482422</v>
@@ -6551,11 +6563,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>141.8974609375</v>
+        <v>141.8974914550781</v>
       </c>
       <c r="C229" t="n">
         <v>152.0599975585938</v>
@@ -6580,7 +6592,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6609,7 +6621,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6638,11 +6650,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>141.1562652587891</v>
+        <v>141.1562805175781</v>
       </c>
       <c r="C232" t="n">
         <v>149.9400024414062</v>
@@ -6667,11 +6679,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>127.6374969482422</v>
+        <v>127.6374816894531</v>
       </c>
       <c r="C233" t="n">
         <v>135.5800018310547</v>
@@ -6696,11 +6708,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>123.7494277954102</v>
+        <v>123.7494201660156</v>
       </c>
       <c r="C234" t="n">
         <v>131.4499969482422</v>
@@ -6725,11 +6737,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>125.6687927246094</v>
+        <v>125.6688003540039</v>
       </c>
       <c r="C235" t="n">
         <v>132.0399932861328</v>
@@ -6754,11 +6766,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>131.2650756835938</v>
+        <v>131.2650909423828</v>
       </c>
       <c r="C236" t="n">
         <v>137.9199981689453</v>
@@ -6783,11 +6795,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>141.4773406982422</v>
+        <v>141.4773254394531</v>
       </c>
       <c r="C237" t="n">
         <v>148.6499938964844</v>
@@ -6812,11 +6824,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>134.9710388183594</v>
+        <v>134.9710235595703</v>
       </c>
       <c r="C238" t="n">
         <v>140.4400024414062</v>
@@ -6841,7 +6853,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6870,7 +6882,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6899,7 +6911,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6928,7 +6940,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6957,11 +6969,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>164.7256011962891</v>
+        <v>164.7256164550781</v>
       </c>
       <c r="C243" t="n">
         <v>169.7400054931641</v>
@@ -6986,7 +6998,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7015,7 +7027,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7044,11 +7056,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>141.1805419921875</v>
+        <v>141.1805572509766</v>
       </c>
       <c r="C246" t="n">
         <v>144.1900024414062</v>
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7102,7 +7114,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7131,7 +7143,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7160,32 +7172,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>130.1799926757812</v>
+        <v>128.1499938964844</v>
       </c>
       <c r="C250" t="n">
-        <v>130.1799926757812</v>
+        <v>128.1499938964844</v>
       </c>
       <c r="D250" t="n">
-        <v>150551200</v>
+        <v>160173800</v>
       </c>
       <c r="E250" t="n">
         <v>7.63</v>
       </c>
       <c r="F250" t="n">
-        <v>17.06159799158339</v>
+        <v>16.79554310569913</v>
       </c>
       <c r="G250" t="n">
         <v>1364891558</v>
       </c>
       <c r="H250" t="n">
-        <v>177681573023.6757</v>
+        <v>174910844827.063</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1103026823761775</v>
+        <v>0.1173527662774217</v>
       </c>
     </row>
   </sheetData>
@@ -7217,75 +7229,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39614</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39697</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40094</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39810</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39893</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39894</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39977</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40379</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39978</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40061</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40094</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40174</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40257</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40258</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40341</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40379</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7531,13 +7543,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40342</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40425</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40458</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7573,13 +7585,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40426</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40537</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7606,7 +7618,7 @@
       <c r="I9" t="n">
         <v>3.91</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K9" t="n">
@@ -7619,13 +7631,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40538</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40621</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7652,7 +7664,7 @@
       <c r="I10" t="n">
         <v>3.73</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="K10" t="n">
@@ -7665,13 +7677,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40622</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40705</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7698,7 +7710,7 @@
       <c r="I11" t="n">
         <v>3.92</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="K11" t="n">
@@ -7711,13 +7723,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40706</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40789</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40828</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7744,7 +7756,7 @@
       <c r="I12" t="n">
         <v>3.98</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40828</v>
       </c>
       <c r="K12" t="n">
@@ -7757,13 +7769,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40790</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7790,7 +7802,7 @@
       <c r="I13" t="n">
         <v>4.03</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K13" t="n">
@@ -7803,13 +7815,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40992</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7836,7 +7848,7 @@
       <c r="I14" t="n">
         <v>4.03</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="K14" t="n">
@@ -7849,13 +7861,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40993</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41076</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7882,7 +7894,7 @@
       <c r="I15" t="n">
         <v>3.8</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="K15" t="n">
@@ -7895,13 +7907,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41077</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41160</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41199</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7928,7 +7940,7 @@
       <c r="I16" t="n">
         <v>3.76</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41199</v>
       </c>
       <c r="K16" t="n">
@@ -7941,13 +7953,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41161</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41272</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7974,7 +7986,7 @@
       <c r="I17" t="n">
         <v>3.92</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="K17" t="n">
@@ -7987,13 +7999,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41273</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41356</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41383</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8020,7 +8032,7 @@
       <c r="I18" t="n">
         <v>3.9</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41383</v>
       </c>
       <c r="K18" t="n">
@@ -8033,13 +8045,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41357</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41440</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8066,7 +8078,7 @@
       <c r="I19" t="n">
         <v>4.24</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="K19" t="n">
@@ -8079,13 +8091,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41441</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41524</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41563</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8112,7 +8124,7 @@
       <c r="I20" t="n">
         <v>4.26</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41563</v>
       </c>
       <c r="K20" t="n">
@@ -8125,13 +8137,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41525</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41636</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8158,7 +8170,7 @@
       <c r="I21" t="n">
         <v>4.32</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="K21" t="n">
@@ -8171,13 +8183,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41637</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41720</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41746</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8204,7 +8216,7 @@
       <c r="I22" t="n">
         <v>4.42</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41746</v>
       </c>
       <c r="K22" t="n">
@@ -8217,13 +8229,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41721</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41804</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8250,7 +8262,7 @@
       <c r="I23" t="n">
         <v>4.43</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="K23" t="n">
@@ -8263,13 +8275,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41805</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41888</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41921</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8296,7 +8308,7 @@
       <c r="I24" t="n">
         <v>4.52</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41921</v>
       </c>
       <c r="K24" t="n">
@@ -8309,13 +8321,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41889</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42000</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8342,7 +8354,7 @@
       <c r="I25" t="n">
         <v>4.27</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="K25" t="n">
@@ -8355,13 +8367,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42001</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42084</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8388,7 +8400,7 @@
       <c r="I26" t="n">
         <v>4.289999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="K26" t="n">
@@ -8401,13 +8413,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42085</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42168</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42194</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8434,7 +8446,7 @@
       <c r="I27" t="n">
         <v>4.33</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42194</v>
       </c>
       <c r="K27" t="n">
@@ -8447,13 +8459,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42169</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42252</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42283</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8480,7 +8492,7 @@
       <c r="I28" t="n">
         <v>3.369999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42283</v>
       </c>
       <c r="K28" t="n">
@@ -8493,13 +8505,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42253</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42364</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8526,7 +8538,7 @@
       <c r="I29" t="n">
         <v>3.67</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K29" t="n">
@@ -8539,13 +8551,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42365</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42448</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42478</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8572,7 +8584,7 @@
       <c r="I30" t="n">
         <v>3.5</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42478</v>
       </c>
       <c r="K30" t="n">
@@ -8585,13 +8597,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42449</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42532</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42558</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8618,7 +8630,7 @@
       <c r="I31" t="n">
         <v>3.55</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42558</v>
       </c>
       <c r="K31" t="n">
@@ -8631,13 +8643,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42533</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42616</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42642</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8664,7 +8676,7 @@
       <c r="I32" t="n">
         <v>4.56</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42642</v>
       </c>
       <c r="K32" t="n">
@@ -8677,13 +8689,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42617</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8710,7 +8722,7 @@
       <c r="I33" t="n">
         <v>4.36</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="K33" t="n">
@@ -8723,13 +8735,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42819</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8756,7 +8768,7 @@
       <c r="I34" t="n">
         <v>4.63</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="K34" t="n">
@@ -8769,13 +8781,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42820</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42903</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42927</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8802,7 +8814,7 @@
       <c r="I35" t="n">
         <v>4.710000000000001</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42927</v>
       </c>
       <c r="K35" t="n">
@@ -8815,13 +8827,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42904</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42987</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43012</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8848,7 +8860,7 @@
       <c r="I36" t="n">
         <v>4.83</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43012</v>
       </c>
       <c r="K36" t="n">
@@ -8861,13 +8873,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42988</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43099</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8894,7 +8906,7 @@
       <c r="I37" t="n">
         <v>3.38</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="K37" t="n">
@@ -8907,13 +8919,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43183</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8940,7 +8952,7 @@
       <c r="I38" t="n">
         <v>3.409999999999999</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K38" t="n">
@@ -8953,13 +8965,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43184</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43267</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43291</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8986,7 +8998,7 @@
       <c r="I39" t="n">
         <v>3.23</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43291</v>
       </c>
       <c r="K39" t="n">
@@ -8999,13 +9011,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43268</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43351</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43375</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9032,7 +9044,7 @@
       <c r="I40" t="n">
         <v>3.489999999999999</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43375</v>
       </c>
       <c r="K40" t="n">
@@ -9045,13 +9057,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43352</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43463</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9078,7 +9090,7 @@
       <c r="I41" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="K41" t="n">
@@ -9091,13 +9103,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43464</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43547</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43572</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9124,7 +9136,7 @@
       <c r="I42" t="n">
         <v>8.84</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43572</v>
       </c>
       <c r="K42" t="n">
@@ -9137,13 +9149,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43548</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43631</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43655</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9170,7 +9182,7 @@
       <c r="I43" t="n">
         <v>9</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43655</v>
       </c>
       <c r="K43" t="n">
@@ -9183,13 +9195,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43632</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43715</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43741</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9216,7 +9228,7 @@
       <c r="I44" t="n">
         <v>8.74</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43741</v>
       </c>
       <c r="K44" t="n">
@@ -9229,13 +9241,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43716</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43827</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9262,7 +9274,7 @@
       <c r="I45" t="n">
         <v>5.2</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="K45" t="n">
@@ -9275,13 +9287,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43828</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43911</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9308,7 +9320,7 @@
       <c r="I46" t="n">
         <v>5.16</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="K46" t="n">
@@ -9321,13 +9333,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43912</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43995</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44025</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9354,7 +9366,7 @@
       <c r="I47" t="n">
         <v>4.9</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44025</v>
       </c>
       <c r="K47" t="n">
@@ -9367,13 +9379,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43996</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44079</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9400,7 +9412,7 @@
       <c r="I48" t="n">
         <v>5.06</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="K48" t="n">
@@ -9413,13 +9425,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44080</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44191</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9446,7 +9458,7 @@
       <c r="I49" t="n">
         <v>5.12</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="K49" t="n">
@@ -9459,13 +9471,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44192</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44275</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44301</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9492,7 +9504,7 @@
       <c r="I50" t="n">
         <v>5.4</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44301</v>
       </c>
       <c r="K50" t="n">
@@ -9505,13 +9517,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44276</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44359</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44390</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9538,7 +9550,7 @@
       <c r="I51" t="n">
         <v>5.92</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44390</v>
       </c>
       <c r="K51" t="n">
@@ -9551,13 +9563,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44360</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44443</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44474</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9584,7 +9596,7 @@
       <c r="I52" t="n">
         <v>5.87</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44474</v>
       </c>
       <c r="K52" t="n">
@@ -9597,13 +9609,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44444</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44555</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44602</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9630,7 +9642,7 @@
       <c r="I53" t="n">
         <v>5.49</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44602</v>
       </c>
       <c r="K53" t="n">
@@ -9643,13 +9655,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44556</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44639</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9676,7 +9688,7 @@
       <c r="I54" t="n">
         <v>7.31</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="K54" t="n">
@@ -9689,13 +9701,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44640</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44723</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44754</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9722,7 +9734,7 @@
       <c r="I55" t="n">
         <v>6.640000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44754</v>
       </c>
       <c r="K55" t="n">
@@ -9735,13 +9747,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44724</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44807</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44846</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9768,7 +9780,7 @@
       <c r="I56" t="n">
         <v>6.99</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44846</v>
       </c>
       <c r="K56" t="n">
@@ -9781,13 +9793,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44808</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9814,7 +9826,7 @@
       <c r="I57" t="n">
         <v>6.42</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="K57" t="n">
@@ -9827,13 +9839,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45010</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9860,7 +9872,7 @@
       <c r="I58" t="n">
         <v>4.76</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="K58" t="n">
@@ -9873,13 +9885,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45011</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45094</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45120</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9906,7 +9918,7 @@
       <c r="I59" t="n">
         <v>5.72</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45120</v>
       </c>
       <c r="K59" t="n">
@@ -9919,13 +9931,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45095</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45178</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45209</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9952,7 +9964,7 @@
       <c r="I60" t="n">
         <v>6.01</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45209</v>
       </c>
       <c r="K60" t="n">
@@ -9965,13 +9977,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45179</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45290</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9998,7 +10010,7 @@
       <c r="I61" t="n">
         <v>6.56</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="K61" t="n">
@@ -10011,13 +10023,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45374</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10044,7 +10056,7 @@
       <c r="I62" t="n">
         <v>6.64</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="K62" t="n">
@@ -10057,13 +10069,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45375</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45458</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45484</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10090,7 +10102,7 @@
       <c r="I63" t="n">
         <v>6.880000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45484</v>
       </c>
       <c r="K63" t="n">
@@ -10103,13 +10115,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45459</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45542</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45573</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10136,7 +10148,7 @@
       <c r="I64" t="n">
         <v>6.77</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45573</v>
       </c>
       <c r="K64" t="n">
@@ -10149,13 +10161,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45543</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45654</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10182,7 +10194,7 @@
       <c r="I65" t="n">
         <v>6.950000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="K65" t="n">
@@ -10195,13 +10207,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45655</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45738</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10228,7 +10240,7 @@
       <c r="I66" t="n">
         <v>6.800000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="K66" t="n">
@@ -10241,13 +10253,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45739</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45822</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10274,7 +10286,7 @@
       <c r="I67" t="n">
         <v>5.490000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="K67" t="n">
@@ -10287,13 +10299,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45823</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45906</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10320,7 +10332,7 @@
       <c r="I68" t="n">
         <v>5.260000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="K68" t="n">
@@ -10333,13 +10345,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45907</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46018</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10366,7 +10378,7 @@
       <c r="I69" t="n">
         <v>6</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="K69" t="n">
@@ -10379,13 +10391,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46019</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10412,7 +10424,7 @@
       <c r="I70" t="n">
         <v>6.37</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="K70" t="n">
@@ -10425,13 +10437,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46186</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46212</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10458,7 +10470,7 @@
       <c r="I71" t="n">
         <v>7.63</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46212</v>
       </c>
       <c r="K71" t="n">
@@ -10495,52 +10507,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40088</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40094</v>
       </c>
       <c r="C2" t="n">
@@ -10569,10 +10581,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40221</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40231</v>
       </c>
       <c r="C3" t="n">
@@ -10601,10 +10613,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40284</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="C4" t="n">
@@ -10633,10 +10645,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40368</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40379</v>
       </c>
       <c r="C5" t="n">
@@ -10665,10 +10677,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40458</v>
       </c>
       <c r="C6" t="n">
@@ -10697,10 +10709,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40585</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C7" t="n">
@@ -10729,10 +10741,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40654</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="C8" t="n">
@@ -10761,10 +10773,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40739</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="C9" t="n">
@@ -10793,10 +10805,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40821</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40828</v>
       </c>
       <c r="C10" t="n">
@@ -10825,10 +10837,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40954</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C11" t="n">
@@ -10857,10 +10869,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41019</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="C12" t="n">
@@ -10889,10 +10901,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41106</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="C13" t="n">
@@ -10921,10 +10933,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41192</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41199</v>
       </c>
       <c r="C14" t="n">
@@ -10953,10 +10965,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41318</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="C15" t="n">
@@ -10985,10 +10997,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41383</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41383</v>
       </c>
       <c r="C16" t="n">
@@ -11017,10 +11029,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41472</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="C17" t="n">
@@ -11049,10 +11061,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41556</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41563</v>
       </c>
       <c r="C18" t="n">
@@ -11081,10 +11093,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41676</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="C19" t="n">
@@ -11113,10 +11125,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41739</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41746</v>
       </c>
       <c r="C20" t="n">
@@ -11145,10 +11157,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41836</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="C21" t="n">
@@ -11177,10 +11189,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41914</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41921</v>
       </c>
       <c r="C22" t="n">
@@ -11209,10 +11221,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42041</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="C23" t="n">
@@ -11241,10 +11253,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42111</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="C24" t="n">
@@ -11273,10 +11285,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42187</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42194</v>
       </c>
       <c r="C25" t="n">
@@ -11305,10 +11317,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42283</v>
       </c>
       <c r="C26" t="n">
@@ -11337,10 +11349,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42404</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C27" t="n">
@@ -11369,10 +11381,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42468</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42478</v>
       </c>
       <c r="C28" t="n">
@@ -11401,10 +11413,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42550</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42558</v>
       </c>
       <c r="C29" t="n">
@@ -11433,10 +11445,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42635</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42642</v>
       </c>
       <c r="C30" t="n">
@@ -11465,10 +11477,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42773</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42781</v>
       </c>
       <c r="C31" t="n">
@@ -11497,10 +11509,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42844</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="C32" t="n">
@@ -11529,10 +11541,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42919</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42927</v>
       </c>
       <c r="C33" t="n">
@@ -11561,10 +11573,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43005</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43012</v>
       </c>
       <c r="C34" t="n">
@@ -11593,10 +11605,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43137</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43144</v>
       </c>
       <c r="C35" t="n">
@@ -11625,10 +11637,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43209</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C36" t="n">
@@ -11657,10 +11669,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43284</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43291</v>
       </c>
       <c r="C37" t="n">
@@ -11689,10 +11701,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43368</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43375</v>
       </c>
       <c r="C38" t="n">
@@ -11721,10 +11733,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43504</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="C39" t="n">
@@ -11753,10 +11765,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43565</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43572</v>
       </c>
       <c r="C40" t="n">
@@ -11785,10 +11797,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43655</v>
       </c>
       <c r="C41" t="n">
@@ -11817,10 +11829,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43734</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43741</v>
       </c>
       <c r="C42" t="n">
@@ -11849,10 +11861,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43867</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="C43" t="n">
@@ -11881,10 +11893,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43942</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="C44" t="n">
@@ -11913,10 +11925,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44018</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44025</v>
       </c>
       <c r="C45" t="n">
@@ -11945,10 +11957,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44098</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="C46" t="n">
@@ -11977,10 +11989,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44231</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="C47" t="n">
@@ -12009,10 +12021,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44294</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44301</v>
       </c>
       <c r="C48" t="n">
@@ -12041,10 +12053,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44383</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44390</v>
       </c>
       <c r="C49" t="n">
@@ -12073,10 +12085,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44467</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44474</v>
       </c>
       <c r="C50" t="n">
@@ -12105,10 +12117,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44595</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44602</v>
       </c>
       <c r="C51" t="n">
@@ -12137,10 +12149,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44670</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="C52" t="n">
@@ -12169,10 +12181,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44747</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44754</v>
       </c>
       <c r="C53" t="n">
@@ -12201,10 +12213,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44839</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44846</v>
       </c>
       <c r="C54" t="n">
@@ -12233,10 +12245,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44959</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="C55" t="n">
@@ -12265,10 +12277,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45034</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="C56" t="n">
@@ -12297,10 +12309,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45113</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45120</v>
       </c>
       <c r="C57" t="n">
@@ -12329,10 +12341,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45202</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45209</v>
       </c>
       <c r="C58" t="n">
@@ -12361,10 +12373,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45324</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="C59" t="n">
@@ -12393,10 +12405,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45398</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="C60" t="n">
@@ -12425,10 +12437,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45478</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45484</v>
       </c>
       <c r="C61" t="n">
@@ -12457,10 +12469,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45573</v>
       </c>
       <c r="C62" t="n">
@@ -12489,10 +12501,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45685</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="C63" t="n">
@@ -12521,10 +12533,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45764</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="C64" t="n">
@@ -12553,10 +12565,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45848</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="C65" t="n">
@@ -12585,10 +12597,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45932</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="C66" t="n">
@@ -12617,10 +12629,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46045</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="C67" t="n">
@@ -12649,10 +12661,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46121</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46128</v>
       </c>
       <c r="C68" t="n">
@@ -12681,10 +12693,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46205</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46212</v>
       </c>
       <c r="C69" t="n">
@@ -12731,12 +12743,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/PEP.xlsx
+++ b/salidas/empresas/PEP.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>31.2156925201416</v>
+        <v>31.21570587158203</v>
       </c>
       <c r="C2" t="n">
         <v>57.18000030517578</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>32.26933670043945</v>
+        <v>32.26932525634766</v>
       </c>
       <c r="C3" t="n">
         <v>59.11000061035156</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>31.68657875061035</v>
+        <v>31.68657493591309</v>
       </c>
       <c r="C4" t="n">
         <v>57.79000091552734</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>31.93331527709961</v>
+        <v>31.93331146240234</v>
       </c>
       <c r="C5" t="n">
         <v>58.2400016784668</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>33.15055465698242</v>
+        <v>33.15055084228516</v>
       </c>
       <c r="C6" t="n">
         <v>60.45999908447266</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.08426284790039</v>
+        <v>33.08425140380859</v>
       </c>
       <c r="C7" t="n">
         <v>60.04000091552734</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>34.92472457885742</v>
+        <v>34.92471694946289</v>
       </c>
       <c r="C8" t="n">
         <v>63.38000106811523</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.97168731689453</v>
+        <v>35.9716911315918</v>
       </c>
       <c r="C9" t="n">
         <v>65.27999877929688</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>34.30561065673828</v>
+        <v>34.30560302734375</v>
       </c>
       <c r="C12" t="n">
         <v>61.97000122070312</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>34.78932952880859</v>
+        <v>34.78931427001953</v>
       </c>
       <c r="C13" t="n">
         <v>62.54999923706055</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>36.28546524047852</v>
+        <v>36.28546905517578</v>
       </c>
       <c r="C14" t="n">
         <v>65.23999786376953</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>35.12303924560547</v>
+        <v>35.12305068969727</v>
       </c>
       <c r="C15" t="n">
         <v>63.15000152587891</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>35.51950073242188</v>
+        <v>35.5195198059082</v>
       </c>
       <c r="C16" t="n">
         <v>63.56000137329102</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>36.44250869750977</v>
+        <v>36.4425163269043</v>
       </c>
       <c r="C19" t="n">
         <v>64.84999847412109</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>36.87522506713867</v>
+        <v>36.87521362304688</v>
       </c>
       <c r="C20" t="n">
         <v>65.62000274658203</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>38.22952651977539</v>
+        <v>38.22951889038086</v>
       </c>
       <c r="C21" t="n">
         <v>68.02999877929688</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>41.39477157592773</v>
+        <v>41.39476013183594</v>
       </c>
       <c r="C22" t="n">
         <v>73.26000213623047</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>41.65470886230469</v>
+        <v>41.65468978881836</v>
       </c>
       <c r="C23" t="n">
         <v>73.72000122070312</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>43.6097297668457</v>
+        <v>43.60970687866211</v>
       </c>
       <c r="C24" t="n">
         <v>77.18000030517578</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>43.09730911254883</v>
+        <v>43.09731292724609</v>
       </c>
       <c r="C25" t="n">
         <v>75.90000152587891</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>38.63996505737305</v>
+        <v>38.63996124267578</v>
       </c>
       <c r="C26" t="n">
         <v>68.05000305175781</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>41.21707153320312</v>
+        <v>41.21707534790039</v>
       </c>
       <c r="C28" t="n">
         <v>72.19999694824219</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>39.12199020385742</v>
+        <v>39.12197494506836</v>
       </c>
       <c r="C29" t="n">
         <v>68.52999877929688</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>38.99067306518555</v>
+        <v>38.99066543579102</v>
       </c>
       <c r="C30" t="n">
         <v>68.30000305175781</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>36.53342056274414</v>
+        <v>36.53341674804688</v>
       </c>
       <c r="C31" t="n">
         <v>63.59000015258789</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>38.23975372314453</v>
+        <v>38.23974227905273</v>
       </c>
       <c r="C32" t="n">
         <v>66.55999755859375</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>39.34281921386719</v>
+        <v>39.34280395507812</v>
       </c>
       <c r="C33" t="n">
         <v>68.48000335693359</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>41.19777297973633</v>
+        <v>41.19777679443359</v>
       </c>
       <c r="C34" t="n">
         <v>71.26999664306641</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>32.95475387573242</v>
+        <v>32.95476150512695</v>
       </c>
       <c r="C35" t="n">
         <v>57.0099983215332</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>32.77555465698242</v>
+        <v>32.77555847167969</v>
       </c>
       <c r="C36" t="n">
         <v>56.70000076293945</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>31.90896606445312</v>
+        <v>31.90897560119629</v>
       </c>
       <c r="C37" t="n">
         <v>54.77000045776367</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>28.04635429382324</v>
+        <v>28.04634666442871</v>
       </c>
       <c r="C39" t="n">
         <v>48.13999938964844</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>30.25754165649414</v>
+        <v>30.25753593444824</v>
       </c>
       <c r="C40" t="n">
         <v>51.47999954223633</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>29.24660301208496</v>
+        <v>29.24659538269043</v>
       </c>
       <c r="C41" t="n">
         <v>49.7599983215332</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>30.59255790710449</v>
+        <v>30.59255027770996</v>
       </c>
       <c r="C42" t="n">
         <v>52.04999923706055</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>32.56758499145508</v>
+        <v>32.56759262084961</v>
       </c>
       <c r="C43" t="n">
         <v>54.95999908447266</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>33.6282844543457</v>
+        <v>33.6283073425293</v>
       </c>
       <c r="C44" t="n">
         <v>56.75</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>33.58090209960938</v>
+        <v>33.58089447021484</v>
       </c>
       <c r="C45" t="n">
         <v>56.66999816894531</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>36.16941833496094</v>
+        <v>36.16941452026367</v>
       </c>
       <c r="C47" t="n">
         <v>60.54999923706055</v>
@@ -1378,7 +1378,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>37.16698837280273</v>
+        <v>37.1669921875</v>
       </c>
       <c r="C48" t="n">
         <v>62.22000122070312</v>
@@ -1403,7 +1403,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>36.57646942138672</v>
+        <v>36.57645034790039</v>
       </c>
       <c r="C49" t="n">
         <v>60.79999923706055</v>
@@ -1428,7 +1428,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>35.8665771484375</v>
+        <v>35.86658096313477</v>
       </c>
       <c r="C50" t="n">
         <v>59.61999893188477</v>
@@ -1453,7 +1453,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>37.58110427856445</v>
+        <v>37.58109664916992</v>
       </c>
       <c r="C51" t="n">
         <v>62.47000122070312</v>
@@ -1503,7 +1503,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>39.5141716003418</v>
+        <v>39.51416397094727</v>
       </c>
       <c r="C53" t="n">
         <v>65.22000122070312</v>
@@ -1553,7 +1553,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>37.21174621582031</v>
+        <v>37.21176528930664</v>
       </c>
       <c r="C55" t="n">
         <v>60.95000076293945</v>
@@ -1578,7 +1578,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>39.62945175170898</v>
+        <v>39.62945556640625</v>
       </c>
       <c r="C56" t="n">
         <v>64.91000366210938</v>
@@ -1628,7 +1628,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>40.86921310424805</v>
+        <v>40.86921691894531</v>
       </c>
       <c r="C58" t="n">
         <v>66.44000244140625</v>
@@ -1653,7 +1653,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>40.16796875</v>
+        <v>40.16797256469727</v>
       </c>
       <c r="C59" t="n">
         <v>65.30000305175781</v>
@@ -1678,7 +1678,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>39.75583267211914</v>
+        <v>39.75582885742188</v>
       </c>
       <c r="C60" t="n">
         <v>64.62999725341797</v>
@@ -1703,7 +1703,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>40.48710250854492</v>
+        <v>40.48711013793945</v>
       </c>
       <c r="C61" t="n">
         <v>65.33000183105469</v>
@@ -1728,7 +1728,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>39.85498046875</v>
+        <v>39.85497665405273</v>
       </c>
       <c r="C62" t="n">
         <v>64.30999755859375</v>
@@ -1753,7 +1753,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>39.30343627929688</v>
+        <v>39.30343246459961</v>
       </c>
       <c r="C63" t="n">
         <v>63.41999816894531</v>
@@ -1811,7 +1811,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>43.02003860473633</v>
+        <v>43.02004241943359</v>
       </c>
       <c r="C65" t="n">
         <v>68.88999938964844</v>
@@ -1840,7 +1840,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>44.41261672973633</v>
+        <v>44.41263198852539</v>
       </c>
       <c r="C66" t="n">
         <v>71.12000274658203</v>
@@ -1869,7 +1869,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>44.30255889892578</v>
+        <v>44.30254364013672</v>
       </c>
       <c r="C67" t="n">
         <v>70.43000030517578</v>
@@ -1898,7 +1898,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>40.28305053710938</v>
+        <v>40.28303909301758</v>
       </c>
       <c r="C68" t="n">
         <v>64.04000091552734</v>
@@ -1927,7 +1927,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>40.85446929931641</v>
+        <v>40.85446166992188</v>
       </c>
       <c r="C69" t="n">
         <v>64.43000030517578</v>
@@ -1956,7 +1956,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>39.25022125244141</v>
+        <v>39.25021362304688</v>
       </c>
       <c r="C70" t="n">
         <v>61.90000152587891</v>
@@ -1985,7 +1985,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>39.9160270690918</v>
+        <v>39.91601181030273</v>
       </c>
       <c r="C71" t="n">
         <v>62.95000076293945</v>
@@ -2043,7 +2043,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>42.4150505065918</v>
+        <v>42.41504287719727</v>
       </c>
       <c r="C73" t="n">
         <v>66.34999847412109</v>
@@ -2072,7 +2072,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.9803581237793</v>
+        <v>41.98036193847656</v>
       </c>
       <c r="C74" t="n">
         <v>65.66999816894531</v>
@@ -2101,7 +2101,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>40.56510162353516</v>
+        <v>40.56509399414062</v>
       </c>
       <c r="C75" t="n">
         <v>62.93999862670898</v>
@@ -2130,7 +2130,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>42.76285934448242</v>
+        <v>42.76284790039062</v>
       </c>
       <c r="C76" t="n">
         <v>66.34999847412109</v>
@@ -2217,7 +2217,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>45.8968391418457</v>
+        <v>45.89683151245117</v>
       </c>
       <c r="C79" t="n">
         <v>70.66000366210938</v>
@@ -2246,7 +2246,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>47.24140930175781</v>
+        <v>47.24138641357422</v>
       </c>
       <c r="C80" t="n">
         <v>72.73000335693359</v>
@@ -2275,7 +2275,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>47.04652786254883</v>
+        <v>47.04650497436523</v>
       </c>
       <c r="C81" t="n">
         <v>72.43000030517578</v>
@@ -2304,7 +2304,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>46.31202697753906</v>
+        <v>46.31204605102539</v>
       </c>
       <c r="C82" t="n">
         <v>70.76999664306641</v>
@@ -2333,7 +2333,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>45.31081390380859</v>
+        <v>45.3108024597168</v>
       </c>
       <c r="C83" t="n">
         <v>69.23999786376953</v>
@@ -2362,7 +2362,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>45.94557571411133</v>
+        <v>45.94557952880859</v>
       </c>
       <c r="C84" t="n">
         <v>70.20999908447266</v>
@@ -2391,7 +2391,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>45.12762069702148</v>
+        <v>45.12761688232422</v>
       </c>
       <c r="C85" t="n">
         <v>68.43000030517578</v>
@@ -2420,7 +2420,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>48.04248809814453</v>
+        <v>48.04249572753906</v>
       </c>
       <c r="C86" t="n">
         <v>72.84999847412109</v>
@@ -2449,7 +2449,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>50.32553100585938</v>
+        <v>50.32550811767578</v>
       </c>
       <c r="C87" t="n">
         <v>75.76999664306641</v>
@@ -2478,7 +2478,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.54389953613281</v>
+        <v>52.54391479492188</v>
       </c>
       <c r="C88" t="n">
         <v>79.11000061035156</v>
@@ -2507,7 +2507,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>54.77559661865234</v>
+        <v>54.77557754516602</v>
       </c>
       <c r="C89" t="n">
         <v>82.47000122070312</v>
@@ -2536,7 +2536,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>53.64646530151367</v>
+        <v>53.64645767211914</v>
       </c>
       <c r="C90" t="n">
         <v>80.76999664306641</v>
@@ -2565,7 +2565,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>54.70458984375</v>
+        <v>54.7045783996582</v>
       </c>
       <c r="C91" t="n">
         <v>81.79000091552734</v>
@@ -2594,7 +2594,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>55.87505340576172</v>
+        <v>55.87506484985352</v>
       </c>
       <c r="C92" t="n">
         <v>83.54000091552734</v>
@@ -2623,7 +2623,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>53.32676315307617</v>
+        <v>53.32677459716797</v>
       </c>
       <c r="C93" t="n">
         <v>79.73000335693359</v>
@@ -2710,7 +2710,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>56.89331817626953</v>
+        <v>56.89332580566406</v>
       </c>
       <c r="C96" t="n">
         <v>84.45999908447266</v>
@@ -2739,7 +2739,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>56.25071716308594</v>
+        <v>56.25070190429688</v>
       </c>
       <c r="C97" t="n">
         <v>82.94000244140625</v>
@@ -2797,7 +2797,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>54.30425643920898</v>
+        <v>54.30422592163086</v>
       </c>
       <c r="C99" t="n">
         <v>80.06999969482422</v>
@@ -2826,7 +2826,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>57.03115081787109</v>
+        <v>57.03117752075195</v>
       </c>
       <c r="C100" t="n">
         <v>83.5</v>
@@ -2855,7 +2855,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>58.66353607177734</v>
+        <v>58.66355514526367</v>
       </c>
       <c r="C101" t="n">
         <v>85.88999938964844</v>
@@ -2884,7 +2884,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>60.3300895690918</v>
+        <v>60.33009338378906</v>
       </c>
       <c r="C102" t="n">
         <v>88.33000183105469</v>
@@ -2913,7 +2913,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>61.47637939453125</v>
+        <v>61.47637557983398</v>
       </c>
       <c r="C103" t="n">
         <v>89.33999633789062</v>
@@ -2942,7 +2942,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>60.62311935424805</v>
+        <v>60.62310028076172</v>
       </c>
       <c r="C104" t="n">
         <v>88.09999847412109</v>
@@ -3000,7 +3000,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>64.51375579833984</v>
+        <v>64.51373291015625</v>
       </c>
       <c r="C106" t="n">
         <v>93.08999633789062</v>
@@ -3029,7 +3029,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>66.64826965332031</v>
+        <v>66.64824676513672</v>
       </c>
       <c r="C107" t="n">
         <v>96.16999816894531</v>
@@ -3058,7 +3058,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>69.37184143066406</v>
+        <v>69.37183380126953</v>
       </c>
       <c r="C108" t="n">
         <v>100.0999984741211</v>
@@ -3087,7 +3087,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>65.96286773681641</v>
+        <v>65.96288299560547</v>
       </c>
       <c r="C109" t="n">
         <v>94.55999755859375</v>
@@ -3116,7 +3116,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>65.41874694824219</v>
+        <v>65.41875457763672</v>
       </c>
       <c r="C110" t="n">
         <v>93.77999877929688</v>
@@ -3145,7 +3145,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>69.04618072509766</v>
+        <v>69.04615020751953</v>
       </c>
       <c r="C111" t="n">
         <v>98.98000335693359</v>
@@ -3174,7 +3174,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>67.14928436279297</v>
+        <v>67.1492919921875</v>
       </c>
       <c r="C112" t="n">
         <v>95.62000274658203</v>
@@ -3203,7 +3203,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>66.79815673828125</v>
+        <v>66.79816436767578</v>
       </c>
       <c r="C113" t="n">
         <v>95.12000274658203</v>
@@ -3232,7 +3232,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>67.71811676025391</v>
+        <v>67.71810913085938</v>
       </c>
       <c r="C114" t="n">
         <v>96.43000030517578</v>
@@ -3261,7 +3261,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>66.03142547607422</v>
+        <v>66.03143310546875</v>
       </c>
       <c r="C115" t="n">
         <v>93.33999633789062</v>
@@ -3290,7 +3290,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>68.1607666015625</v>
+        <v>68.16078186035156</v>
       </c>
       <c r="C116" t="n">
         <v>96.34999847412109</v>
@@ -3319,7 +3319,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>65.74139404296875</v>
+        <v>65.74136352539062</v>
       </c>
       <c r="C117" t="n">
         <v>92.93000030517578</v>
@@ -3377,7 +3377,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>72.85294342041016</v>
+        <v>72.85295867919922</v>
       </c>
       <c r="C119" t="n">
         <v>102.1900024414062</v>
@@ -3406,7 +3406,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>71.40570068359375</v>
+        <v>71.40572357177734</v>
       </c>
       <c r="C120" t="n">
         <v>100.1600036621094</v>
@@ -3435,7 +3435,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>71.733642578125</v>
+        <v>71.73365020751953</v>
       </c>
       <c r="C121" t="n">
         <v>99.91999816894531</v>
@@ -3493,7 +3493,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>70.22602081298828</v>
+        <v>70.22600555419922</v>
       </c>
       <c r="C123" t="n">
         <v>97.81999969482422</v>
@@ -3522,7 +3522,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>74.09714508056641</v>
+        <v>74.09717559814453</v>
       </c>
       <c r="C124" t="n">
         <v>102.4800033569336</v>
@@ -3551,7 +3551,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>74.44425201416016</v>
+        <v>74.44420623779297</v>
       </c>
       <c r="C125" t="n">
         <v>102.9599990844727</v>
@@ -3609,7 +3609,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>77.17329406738281</v>
+        <v>77.17330169677734</v>
       </c>
       <c r="C127" t="n">
         <v>105.9400024414062</v>
@@ -3638,7 +3638,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>79.34410858154297</v>
+        <v>79.34409332275391</v>
       </c>
       <c r="C128" t="n">
         <v>108.9199981689453</v>
@@ -3696,7 +3696,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>79.79527282714844</v>
+        <v>79.79526519775391</v>
       </c>
       <c r="C130" t="n">
         <v>108.7699966430664</v>
@@ -3725,7 +3725,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>78.64347839355469</v>
+        <v>78.64350128173828</v>
       </c>
       <c r="C131" t="n">
         <v>107.1999969482422</v>
@@ -3754,7 +3754,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>73.97810363769531</v>
+        <v>73.97808074951172</v>
       </c>
       <c r="C132" t="n">
         <v>100.0999984741211</v>
@@ -3783,7 +3783,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>77.32595825195312</v>
+        <v>77.32594299316406</v>
       </c>
       <c r="C133" t="n">
         <v>104.629997253418</v>
@@ -3812,7 +3812,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>76.69775390625</v>
+        <v>76.69776916503906</v>
       </c>
       <c r="C134" t="n">
         <v>103.7799987792969</v>
@@ -3841,7 +3841,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>81.575439453125</v>
+        <v>81.57545471191406</v>
       </c>
       <c r="C135" t="n">
         <v>110.379997253418</v>
@@ -3899,7 +3899,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>84.29370880126953</v>
+        <v>84.29372406005859</v>
       </c>
       <c r="C137" t="n">
         <v>113.2799987792969</v>
@@ -3928,7 +3928,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>87.56240081787109</v>
+        <v>87.56240844726562</v>
       </c>
       <c r="C138" t="n">
         <v>116.870002746582</v>
@@ -3957,7 +3957,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>86.52845764160156</v>
+        <v>86.52842712402344</v>
       </c>
       <c r="C139" t="n">
         <v>115.4899978637695</v>
@@ -3986,7 +3986,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>87.36759185791016</v>
+        <v>87.36758422851562</v>
       </c>
       <c r="C140" t="n">
         <v>116.6100006103516</v>
@@ -4044,7 +4044,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>84.07082366943359</v>
+        <v>84.07080841064453</v>
       </c>
       <c r="C142" t="n">
         <v>111.4300003051758</v>
@@ -4073,7 +4073,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>83.16547393798828</v>
+        <v>83.16546630859375</v>
       </c>
       <c r="C143" t="n">
         <v>110.2300033569336</v>
@@ -4102,7 +4102,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>88.52095031738281</v>
+        <v>88.52095794677734</v>
       </c>
       <c r="C144" t="n">
         <v>116.5199966430664</v>
@@ -4131,7 +4131,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>91.10396575927734</v>
+        <v>91.10398101806641</v>
       </c>
       <c r="C145" t="n">
         <v>119.9199981689453</v>
@@ -4160,7 +4160,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>91.39267730712891</v>
+        <v>91.39266204833984</v>
       </c>
       <c r="C146" t="n">
         <v>120.3000030517578</v>
@@ -4189,7 +4189,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>83.36257934570312</v>
+        <v>83.36256408691406</v>
       </c>
       <c r="C147" t="n">
         <v>109.7300033569336</v>
@@ -4247,7 +4247,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>77.25150299072266</v>
+        <v>77.25149536132812</v>
       </c>
       <c r="C149" t="n">
         <v>100.9400024414062</v>
@@ -4276,7 +4276,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>77.42903137207031</v>
+        <v>77.42906188964844</v>
       </c>
       <c r="C150" t="n">
         <v>100.25</v>
@@ -4305,7 +4305,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>84.08676147460938</v>
+        <v>84.08676910400391</v>
       </c>
       <c r="C151" t="n">
         <v>108.870002746582</v>
@@ -4334,7 +4334,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>88.82133483886719</v>
+        <v>88.82134246826172</v>
       </c>
       <c r="C152" t="n">
         <v>115</v>
@@ -4363,7 +4363,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>86.51197052001953</v>
+        <v>86.51197814941406</v>
       </c>
       <c r="C153" t="n">
         <v>112.0100021362305</v>
@@ -4392,7 +4392,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>87.06404113769531</v>
+        <v>87.06403350830078</v>
       </c>
       <c r="C154" t="n">
         <v>111.8000030517578</v>
@@ -4450,7 +4450,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>94.96056365966797</v>
+        <v>94.96054077148438</v>
       </c>
       <c r="C156" t="n">
         <v>121.9400024414062</v>
@@ -4479,7 +4479,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>86.71923065185547</v>
+        <v>86.71924591064453</v>
       </c>
       <c r="C157" t="n">
         <v>110.4800033569336</v>
@@ -4508,7 +4508,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>88.438232421875</v>
+        <v>88.43824005126953</v>
       </c>
       <c r="C158" t="n">
         <v>112.6699981689453</v>
@@ -4537,7 +4537,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>91.50554656982422</v>
+        <v>91.50553131103516</v>
       </c>
       <c r="C159" t="n">
         <v>115.6399993896484</v>
@@ -4595,7 +4595,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>101.3255233764648</v>
+        <v>101.3255310058594</v>
       </c>
       <c r="C161" t="n">
         <v>128.0500030517578</v>
@@ -4624,7 +4624,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>101.2859573364258</v>
+        <v>101.2859649658203</v>
       </c>
       <c r="C162" t="n">
         <v>128</v>
@@ -4682,7 +4682,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>101.876091003418</v>
+        <v>101.8760833740234</v>
       </c>
       <c r="C164" t="n">
         <v>127.8099975585938</v>
@@ -4711,7 +4711,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>108.9861297607422</v>
+        <v>108.9861221313477</v>
       </c>
       <c r="C165" t="n">
         <v>136.7299957275391</v>
@@ -4769,7 +4769,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>110.0924301147461</v>
+        <v>110.0924224853516</v>
       </c>
       <c r="C167" t="n">
         <v>137.1699981689453</v>
@@ -4827,7 +4827,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>110.4594268798828</v>
+        <v>110.4594497680664</v>
       </c>
       <c r="C169" t="n">
         <v>136.6699981689453</v>
@@ -4856,7 +4856,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>114.7833938598633</v>
+        <v>114.7834320068359</v>
       </c>
       <c r="C170" t="n">
         <v>142.0200042724609</v>
@@ -4885,7 +4885,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>106.7092971801758</v>
+        <v>106.7092895507812</v>
       </c>
       <c r="C171" t="n">
         <v>132.0299987792969</v>
@@ -4943,7 +4943,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>107.6413803100586</v>
+        <v>107.6413955688477</v>
       </c>
       <c r="C173" t="n">
         <v>132.2899932861328</v>
@@ -4972,7 +4972,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>107.0392608642578</v>
+        <v>107.0392456054688</v>
       </c>
       <c r="C174" t="n">
         <v>131.5500030517578</v>
@@ -5001,7 +5001,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>108.4522933959961</v>
+        <v>108.452262878418</v>
       </c>
       <c r="C175" t="n">
         <v>132.2599945068359</v>
@@ -5030,7 +5030,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>112.8802642822266</v>
+        <v>112.880256652832</v>
       </c>
       <c r="C176" t="n">
         <v>137.6600036621094</v>
@@ -5088,7 +5088,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>114.4682693481445</v>
+        <v>114.4682922363281</v>
       </c>
       <c r="C178" t="n">
         <v>138.6000061035156</v>
@@ -5175,7 +5175,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>123.3519287109375</v>
+        <v>123.3519515991211</v>
       </c>
       <c r="C181" t="n">
         <v>148.3000030517578</v>
@@ -5204,7 +5204,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>113.5952453613281</v>
+        <v>113.5952606201172</v>
       </c>
       <c r="C182" t="n">
         <v>136.5700073242188</v>
@@ -5233,7 +5233,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>107.4567565917969</v>
+        <v>107.4567718505859</v>
       </c>
       <c r="C183" t="n">
         <v>129.1900024414062</v>
@@ -5262,7 +5262,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>118.5937881469727</v>
+        <v>118.5937576293945</v>
       </c>
       <c r="C184" t="n">
         <v>141.4499969482422</v>
@@ -5291,7 +5291,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>120.8658981323242</v>
+        <v>120.865837097168</v>
       </c>
       <c r="C185" t="n">
         <v>144.1600036621094</v>
@@ -5320,7 +5320,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>124.0350723266602</v>
+        <v>124.0350952148438</v>
       </c>
       <c r="C186" t="n">
         <v>147.9400024414062</v>
@@ -5349,7 +5349,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>125.135498046875</v>
+        <v>125.1354827880859</v>
       </c>
       <c r="C187" t="n">
         <v>148.1699981689453</v>
@@ -5378,7 +5378,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>132.5505523681641</v>
+        <v>132.550537109375</v>
       </c>
       <c r="C188" t="n">
         <v>156.9499969482422</v>
@@ -5407,7 +5407,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>132.0776062011719</v>
+        <v>132.0776214599609</v>
       </c>
       <c r="C189" t="n">
         <v>156.3899993896484</v>
@@ -5436,7 +5436,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>127.8979797363281</v>
+        <v>127.8979568481445</v>
       </c>
       <c r="C190" t="n">
         <v>150.4100036621094</v>
@@ -5465,7 +5465,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>137.4131469726562</v>
+        <v>137.4131317138672</v>
       </c>
       <c r="C191" t="n">
         <v>161.6000061035156</v>
@@ -5494,7 +5494,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>135.8655242919922</v>
+        <v>135.8655395507812</v>
       </c>
       <c r="C192" t="n">
         <v>159.7799987792969</v>
@@ -5523,7 +5523,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>148.708740234375</v>
+        <v>148.7087707519531</v>
       </c>
       <c r="C193" t="n">
         <v>173.7100067138672</v>
@@ -5581,7 +5581,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>140.1736907958984</v>
+        <v>140.1736755371094</v>
       </c>
       <c r="C195" t="n">
         <v>163.7400054931641</v>
@@ -5639,7 +5639,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>147.9634246826172</v>
+        <v>147.9634399414062</v>
       </c>
       <c r="C197" t="n">
         <v>171.7100067138672</v>
@@ -5668,7 +5668,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>144.5510559082031</v>
+        <v>144.5510864257812</v>
       </c>
       <c r="C198" t="n">
         <v>167.75</v>
@@ -5697,7 +5697,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>144.6106872558594</v>
+        <v>144.6107025146484</v>
       </c>
       <c r="C199" t="n">
         <v>166.6600036621094</v>
@@ -5726,7 +5726,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>151.8125762939453</v>
+        <v>151.8125610351562</v>
       </c>
       <c r="C200" t="n">
         <v>174.9600067138672</v>
@@ -5755,7 +5755,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>149.4784851074219</v>
+        <v>149.4784698486328</v>
       </c>
       <c r="C201" t="n">
         <v>172.2700042724609</v>
@@ -5813,7 +5813,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>158.6156158447266</v>
+        <v>158.6155853271484</v>
       </c>
       <c r="C203" t="n">
         <v>181.5800018310547</v>
@@ -5842,7 +5842,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>162.0485992431641</v>
+        <v>162.0485534667969</v>
       </c>
       <c r="C204" t="n">
         <v>185.5099945068359</v>
@@ -5900,7 +5900,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>150.3229827880859</v>
+        <v>150.3230285644531</v>
       </c>
       <c r="C206" t="n">
         <v>171.0200042724609</v>
@@ -5929,7 +5929,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>152.5292358398438</v>
+        <v>152.5292510986328</v>
       </c>
       <c r="C207" t="n">
         <v>173.5299987792969</v>
@@ -5958,7 +5958,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>161.3207092285156</v>
+        <v>161.3206787109375</v>
       </c>
       <c r="C208" t="n">
         <v>182.3000030517578</v>
@@ -5987,7 +5987,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>168.9221496582031</v>
+        <v>168.9221343994141</v>
       </c>
       <c r="C209" t="n">
         <v>190.8899993896484</v>
@@ -6045,7 +6045,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>165.0496520996094</v>
+        <v>165.0496368408203</v>
       </c>
       <c r="C211" t="n">
         <v>185.2200012207031</v>
@@ -6074,7 +6074,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>167.0456695556641</v>
+        <v>167.0457000732422</v>
       </c>
       <c r="C212" t="n">
         <v>187.4600067138672</v>
@@ -6103,7 +6103,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>159.6599578857422</v>
+        <v>159.6599426269531</v>
       </c>
       <c r="C213" t="n">
         <v>177.9199981689453</v>
@@ -6161,7 +6161,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>146.5224609375</v>
+        <v>146.5224761962891</v>
       </c>
       <c r="C215" t="n">
         <v>163.2799987792969</v>
@@ -6190,7 +6190,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>152.1698455810547</v>
+        <v>152.1698303222656</v>
       </c>
       <c r="C216" t="n">
         <v>168.2899932861328</v>
@@ -6219,7 +6219,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>153.5713653564453</v>
+        <v>153.5713806152344</v>
       </c>
       <c r="C217" t="n">
         <v>169.8399963378906</v>
@@ -6248,7 +6248,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>152.3868865966797</v>
+        <v>152.3868560791016</v>
       </c>
       <c r="C218" t="n">
         <v>168.5299987792969</v>
@@ -6277,7 +6277,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>150.6433258056641</v>
+        <v>150.643310546875</v>
       </c>
       <c r="C219" t="n">
         <v>165.3399963378906</v>
@@ -6335,7 +6335,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>160.2737731933594</v>
+        <v>160.2737579345703</v>
       </c>
       <c r="C221" t="n">
         <v>175.9100036621094</v>
@@ -6364,7 +6364,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>157.5313110351562</v>
+        <v>157.5313415527344</v>
       </c>
       <c r="C222" t="n">
         <v>172.8999938964844</v>
@@ -6393,7 +6393,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>151.4546661376953</v>
+        <v>151.4546356201172</v>
       </c>
       <c r="C223" t="n">
         <v>164.9299926757812</v>
@@ -6451,7 +6451,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>158.7550964355469</v>
+        <v>158.7550811767578</v>
       </c>
       <c r="C225" t="n">
         <v>172.8800048828125</v>
@@ -6480,7 +6480,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>157.3453979492188</v>
+        <v>157.3454132080078</v>
       </c>
       <c r="C226" t="n">
         <v>170.0500030517578</v>
@@ -6567,7 +6567,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>141.8974914550781</v>
+        <v>141.8974761962891</v>
       </c>
       <c r="C229" t="n">
         <v>152.0599975585938</v>
@@ -6596,7 +6596,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>140.6190338134766</v>
+        <v>140.6190490722656</v>
       </c>
       <c r="C230" t="n">
         <v>150.6900024414062</v>
@@ -6654,7 +6654,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>141.1562805175781</v>
+        <v>141.15625</v>
       </c>
       <c r="C232" t="n">
         <v>149.9400024414062</v>
@@ -6683,7 +6683,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>127.6374816894531</v>
+        <v>127.6375045776367</v>
       </c>
       <c r="C233" t="n">
         <v>135.5800018310547</v>
@@ -6712,7 +6712,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>123.7494201660156</v>
+        <v>123.7494277954102</v>
       </c>
       <c r="C234" t="n">
         <v>131.4499969482422</v>
@@ -6741,7 +6741,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>125.6688003540039</v>
+        <v>125.6687927246094</v>
       </c>
       <c r="C235" t="n">
         <v>132.0399932861328</v>
@@ -6770,7 +6770,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>131.2650909423828</v>
+        <v>131.2650756835938</v>
       </c>
       <c r="C236" t="n">
         <v>137.9199981689453</v>
@@ -6799,7 +6799,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>141.4773254394531</v>
+        <v>141.4773559570312</v>
       </c>
       <c r="C237" t="n">
         <v>148.6499938964844</v>
@@ -6915,7 +6915,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>139.2801971435547</v>
+        <v>139.2801818847656</v>
       </c>
       <c r="C241" t="n">
         <v>143.5200042724609</v>
@@ -6973,7 +6973,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>164.7256164550781</v>
+        <v>164.7256011962891</v>
       </c>
       <c r="C243" t="n">
         <v>169.7400054931641</v>
@@ -7060,7 +7060,7 @@
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>141.1805572509766</v>
+        <v>141.1805419921875</v>
       </c>
       <c r="C246" t="n">
         <v>144.1900024414062</v>
